--- a/PCB/PickAndPlace.xlsx
+++ b/PCB/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2024-12-13" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2025-01-12" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="104">
   <si>
     <t>Designator</t>
   </si>
@@ -254,6 +254,75 @@
   </si>
   <si>
     <t>21.801mm</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>BSMD0603-075-6V</t>
+  </si>
+  <si>
+    <t>F0603</t>
+  </si>
+  <si>
+    <t>63.246mm</t>
+  </si>
+  <si>
+    <t>13.97mm</t>
+  </si>
+  <si>
+    <t>63.999mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>WNM2020-3/TR-VB</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P0.95-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>69.342mm</t>
+  </si>
+  <si>
+    <t>14.478mm</t>
+  </si>
+  <si>
+    <t>68.342mm</t>
+  </si>
+  <si>
+    <t>13.528mm</t>
+  </si>
+  <si>
+    <t>VSEL</t>
+  </si>
+  <si>
+    <t>SK-3293S</t>
+  </si>
+  <si>
+    <t>SW-SMD_SK-3293S</t>
+  </si>
+  <si>
+    <t>76.631mm</t>
+  </si>
+  <si>
+    <t>16.141mm</t>
+  </si>
+  <si>
+    <t>76.366mm</t>
+  </si>
+  <si>
+    <t>16.411mm</t>
+  </si>
+  <si>
+    <t>76.046mm</t>
+  </si>
+  <si>
+    <t>18.166mm</t>
   </si>
 </sst>
 </file>
@@ -630,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -1164,6 +1233,138 @@
         <v>49</v>
       </c>
     </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13">
+        <v>180</v>
+      </c>
+      <c r="M13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" t="s">
+        <v>94</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14">
+        <v>180</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" t="s">
+        <v>103</v>
+      </c>
+      <c r="J15">
+        <v>7</v>
+      </c>
+      <c r="K15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15">
+        <v>224.442</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
